--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260819.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260819.xlsx
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>41,037,000</t>
+          <t>15,188,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>15,188,000</t>
+          <t>41,037,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
